--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/ARKANSAS_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/ARKANSAS_2024.xlsx
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C151">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C250">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C565">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C670">
